--- a/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CCBC643-29CB-4106-9135-CDC66F1BBF75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94F56E7-1284-4CE2-BF0C-D3575F79981F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CF0E73-BF57-4A1E-96A5-B6650C7CE228}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B619EC4-C70C-4B24-A1E4-4A9C8111A2CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FD1DEAB-1DBD-4094-9E88-5E5DD6E0B6B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003FFD74-1832-4AC7-9F4B-8FD20933644F}"/>
 </file>